--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96567</v>
+        <v>96570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89314</v>
+        <v>89316</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96570</v>
+        <v>96571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96571</v>
+        <v>96576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96576</v>
+        <v>96578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89318</v>
+        <v>89320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Fogelström, Uno Pettersson, Per Darell</t>
+          <t>Per Darell, Uno Pettersson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -894,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Darell, Uno Pettersson, Per Fogelström</t>
+          <t>Per Fogelström, Uno Pettersson, Per Darell</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96578</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89320</v>
+        <v>89322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89322</v>
+        <v>89324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -894,7 +894,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Fogelström, Uno Pettersson, Per Darell</t>
+          <t>Per Darell, Uno Pettersson, Per Fogelström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136447739</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89324</v>
+        <v>89325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35257-2026 artfynd.xlsx
+++ b/artfynd/A 35257-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>136448808</v>
       </c>
       <c r="B3" t="n">
-        <v>89325</v>
+        <v>89331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
